--- a/data/trans_camb/DCD-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 6,03</t>
+          <t>-1,56; 6,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 9,27</t>
+          <t>1,81; 9,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 10,03</t>
+          <t>-4,0; 9,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 4,36</t>
+          <t>-7,84; 4,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 6,61</t>
+          <t>-1,6; 6,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,66</t>
+          <t>-1,71; 5,59</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 254,88</t>
+          <t>-34,84; 284,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,5; 400,96</t>
+          <t>24,47; 416,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 68,38</t>
+          <t>-18,82; 67,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 30,41</t>
+          <t>-34,71; 29,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 78,33</t>
+          <t>-13,55; 69,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 65,28</t>
+          <t>-12,14; 64,23</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,13</t>
+          <t>-4,57; 1,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,87</t>
+          <t>1,42; 9,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -3,36</t>
+          <t>-11,53; -3,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,92</t>
+          <t>8,03; 17,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,93</t>
+          <t>-7,04; -1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,23</t>
+          <t>6,27; 12,18</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,08; 31,18</t>
+          <t>-60,94; 39,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,31; 233,12</t>
+          <t>11,94; 214,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,85; -25,53</t>
+          <t>-68,07; -26,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,64; 139,87</t>
+          <t>45,56; 143,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,89; -21,67</t>
+          <t>-59,74; -21,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,72; 138,95</t>
+          <t>53,14; 133,61</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,96</t>
+          <t>-3,93; 3,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 13,94</t>
+          <t>5,01; 13,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 5,21</t>
+          <t>-5,4; 5,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 18,47</t>
+          <t>7,55; 18,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,12</t>
+          <t>-3,77; 2,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 15,12</t>
+          <t>8,05; 15,23</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 81,5</t>
+          <t>-53,83; 89,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,3; 364,03</t>
+          <t>54,29; 369,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 50,78</t>
+          <t>-35,09; 51,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47,25; 193,05</t>
+          <t>45,83; 192,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 42,92</t>
+          <t>-33,71; 38,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,48; 203,28</t>
+          <t>68,91; 211,09</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,28</t>
+          <t>-2,64; 6,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 12,03</t>
+          <t>2,01; 12,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 3,9</t>
+          <t>-7,28; 4,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 9,47</t>
+          <t>-7,23; 9,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 3,38</t>
+          <t>-3,5; 3,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 9,56</t>
+          <t>-0,58; 9,55</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,05; 90,95</t>
+          <t>-27,3; 111,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,27; 214,18</t>
+          <t>18,97; 222,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 25,39</t>
+          <t>-34,15; 26,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 54,0</t>
+          <t>-31,69; 54,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 29,6</t>
+          <t>-23,9; 28,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 80,05</t>
+          <t>-4,53; 75,68</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 0,95</t>
+          <t>-11,76; 0,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 2,27</t>
+          <t>-10,19; 2,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,84; -8,18</t>
+          <t>-24,75; -8,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-26,8; -8,56</t>
+          <t>-27,89; -8,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -5,92</t>
+          <t>-16,5; -5,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,14; -4,71</t>
+          <t>-15,82; -4,19</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,79; 12,43</t>
+          <t>-67,25; 10,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,37; 25,42</t>
+          <t>-55,28; 28,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,7; -27,05</t>
+          <t>-65,7; -26,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,44; -30,69</t>
+          <t>-74,07; -30,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -27,14</t>
+          <t>-62,78; -28,36</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,8; -23,4</t>
+          <t>-60,49; -22,26</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 0,94</t>
+          <t>-8,74; 0,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,35; 12,63</t>
+          <t>2,12; 12,85</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 2,79</t>
+          <t>-8,92; 3,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10,22; 23,45</t>
+          <t>9,67; 22,9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 0,77</t>
+          <t>-7,64; 0,36</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,21; 16,01</t>
+          <t>7,71; 16,52</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 13,43</t>
+          <t>-64,59; 14,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6,98; 149,73</t>
+          <t>13,11; 153,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-45,61; 22,16</t>
+          <t>-46,88; 34,67</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49,5; 176,13</t>
+          <t>45,67; 176,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 9,31</t>
+          <t>-47,86; 3,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44,8; 140,55</t>
+          <t>46,85; 145,08</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,87</t>
+          <t>-1,14; 4,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,66</t>
+          <t>6,76; 13,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 0,9</t>
+          <t>-7,28; 0,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 21,44</t>
+          <t>-2,81; 21,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,61</t>
+          <t>-3,24; 1,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,2; 16,25</t>
+          <t>2,76; 16,32</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 104,16</t>
+          <t>-15,87; 92,24</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>86,75; 281,04</t>
+          <t>88,55; 277,31</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 7,64</t>
+          <t>-41,36; 7,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 148,27</t>
+          <t>-16,54; 143,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 17,11</t>
+          <t>-26,34; 18,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,61; 158,63</t>
+          <t>25,68; 160,1</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,98</t>
+          <t>-1,03; 3,69</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 6,04</t>
+          <t>-2,67; 6,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 1,45</t>
+          <t>-5,54; 1,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6,09; 13,18</t>
+          <t>5,55; 12,8</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,82</t>
+          <t>-2,45; 1,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 8,18</t>
+          <t>-1,31; 8,18</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 94,39</t>
+          <t>-16,99; 88,33</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 122,51</t>
+          <t>-40,54; 127,64</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 13,0</t>
+          <t>-36,5; 13,31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41,02; 119,52</t>
+          <t>37,56; 114,85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 22,74</t>
+          <t>-24,38; 21,11</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 92,86</t>
+          <t>-11,34; 94,23</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,27</t>
+          <t>-1,14; 1,35</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,39</t>
+          <t>3,17; 7,52</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -1,64</t>
+          <t>-4,89; -1,35</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,33</t>
+          <t>3,34; 10,44</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,65; -0,52</t>
+          <t>-2,7; -0,54</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,52</t>
+          <t>4,33; 8,54</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 21,11</t>
+          <t>-15,52; 22,46</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>43,17; 120,6</t>
+          <t>47,99; 122,91</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,28; -10,49</t>
+          <t>-28,61; -8,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>20,95; 66,58</t>
+          <t>20,81; 66,42</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-22,3; -5,09</t>
+          <t>-22,25; -4,52</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>39,12; 76,38</t>
+          <t>36,65; 77,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DCD-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,68</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>2,4</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 6,13</t>
+          <t>-1,44; 6,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,5</t>
+          <t>1,81; 9,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 9,9</t>
+          <t>-3,82; 10,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 4,11</t>
+          <t>-7,23; 4,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 6,53</t>
+          <t>-1,04; 7,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 5,59</t>
+          <t>-1,53; 5,88</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>152,02%</t>
+          <t>153,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,06%</t>
+          <t>-5,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 284,13</t>
+          <t>-32,23; 250,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,47; 416,77</t>
+          <t>29,03; 415,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 67,9</t>
+          <t>-18,16; 71,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 29,48</t>
+          <t>-31,89; 28,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 69,26</t>
+          <t>-9,13; 75,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 64,23</t>
+          <t>-12,0; 67,57</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,67</t>
+          <t>12,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>9,07</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,29</t>
+          <t>-4,71; 1,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 9,53</t>
+          <t>1,79; 9,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -3,46</t>
+          <t>-11,02; -3,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 17,38</t>
+          <t>7,85; 16,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,04; -1,91</t>
+          <t>-7,05; -2,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 12,18</t>
+          <t>5,98; 12,32</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>100,84%</t>
+          <t>102,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 39,83</t>
+          <t>-60,31; 35,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,94; 214,51</t>
+          <t>20,32; 227,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,07; -26,32</t>
+          <t>-66,21; -27,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,56; 143,51</t>
+          <t>45,86; 141,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,74; -21,58</t>
+          <t>-59,84; -22,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,14; 133,61</t>
+          <t>50,3; 136,57</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9,5</t>
+          <t>9,2</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,33</t>
+          <t>13,27</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,59</t>
+          <t>11,48</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,2</t>
+          <t>-4,49; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 13,99</t>
+          <t>4,8; 13,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 5,22</t>
+          <t>-5,57; 5,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 18,69</t>
+          <t>7,87; 18,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 2,94</t>
+          <t>-3,4; 2,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,05; 15,23</t>
+          <t>8,0; 15,07</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>170,2%</t>
+          <t>164,91%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105,82%</t>
+          <t>105,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>126,33%</t>
+          <t>125,11%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,83; 89,49</t>
+          <t>-54,57; 82,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54,29; 369,84</t>
+          <t>52,37; 354,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 51,02</t>
+          <t>-37,2; 59,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45,83; 192,66</t>
+          <t>44,97; 186,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,71; 38,09</t>
+          <t>-31,27; 39,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,91; 211,09</t>
+          <t>68,14; 203,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>7,37</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>6,81</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,1</t>
+          <t>-2,65; 5,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 12,07</t>
+          <t>0,97; 10,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 4,44</t>
+          <t>-7,11; 3,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 9,71</t>
+          <t>1,86; 12,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,39</t>
+          <t>-4,0; 3,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 9,55</t>
+          <t>2,74; 10,32</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 111,92</t>
+          <t>-29,32; 103,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,97; 222,95</t>
+          <t>8,1; 179,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 26,74</t>
+          <t>-32,67; 22,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 54,67</t>
+          <t>7,22; 76,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 28,68</t>
+          <t>-25,76; 27,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 75,68</t>
+          <t>16,21; 86,59</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-3,46</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-16,62</t>
+          <t>-13,76</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-9,62</t>
+          <t>-8,91</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 0,9</t>
+          <t>-11,54; 0,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 2,66</t>
+          <t>-10,36; 1,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,75; -8,1</t>
+          <t>-24,6; -8,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-27,89; -8,63</t>
+          <t>-20,66; -7,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -5,89</t>
+          <t>-16,37; -6,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,82; -4,19</t>
+          <t>-13,71; -3,94</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-25,35%</t>
+          <t>-31,4%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-50,26%</t>
+          <t>-41,61%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-40,93%</t>
+          <t>-37,91%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,25; 10,75</t>
+          <t>-67,2; 7,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 28,79</t>
+          <t>-60,51; 17,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,7; -26,73</t>
+          <t>-64,54; -27,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,07; -30,29</t>
+          <t>-54,85; -24,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-62,78; -28,36</t>
+          <t>-61,65; -28,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,49; -22,26</t>
+          <t>-51,06; -19,95</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16,56</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,88</t>
+          <t>11,74</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 0,95</t>
+          <t>-8,95; 1,37</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,85</t>
+          <t>1,92; 12,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 3,96</t>
+          <t>-8,81; 3,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9,67; 22,9</t>
+          <t>9,26; 22,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 0,36</t>
+          <t>-7,49; 0,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,71; 16,52</t>
+          <t>7,38; 15,5</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101,25%</t>
+          <t>100,26%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-64,59; 14,28</t>
+          <t>-64,97; 21,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13,11; 153,82</t>
+          <t>11,17; 156,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 34,67</t>
+          <t>-46,61; 27,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45,67; 176,17</t>
+          <t>45,71; 175,37</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 3,07</t>
+          <t>-47,41; 5,17</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46,85; 145,08</t>
+          <t>44,32; 134,02</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10,07</t>
+          <t>10,08</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11,66</t>
+          <t>20,85</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,6</t>
+          <t>15,72</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,56</t>
+          <t>-0,88; 4,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,76; 13,85</t>
+          <t>6,53; 13,31</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 0,96</t>
+          <t>-6,7; 0,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 21,21</t>
+          <t>16,21; 25,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,74</t>
+          <t>-2,96; 1,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,76; 16,32</t>
+          <t>12,6; 18,51</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>165,27%</t>
+          <t>165,49%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>134,48%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>106,31%</t>
+          <t>144,08%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 92,24</t>
+          <t>-14,01; 96,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>88,55; 277,31</t>
+          <t>83,82; 267,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 7,43</t>
+          <t>-40,02; 5,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 143,56</t>
+          <t>89,96; 193,04</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 18,0</t>
+          <t>-24,72; 18,33</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,68; 160,1</t>
+          <t>101,88; 194,98</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>8,76</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>6,8</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,69</t>
+          <t>-1,35; 3,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 6,15</t>
+          <t>2,28; 7,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 1,58</t>
+          <t>-4,94; 1,67</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5,55; 12,8</t>
+          <t>5,41; 12,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,72</t>
+          <t>-2,32; 1,75</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 8,18</t>
+          <t>4,57; 9,0</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 88,33</t>
+          <t>-21,68; 80,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 127,64</t>
+          <t>33,81; 172,59</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 13,31</t>
+          <t>-33,86; 15,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>37,56; 114,85</t>
+          <t>35,58; 110,23</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 21,11</t>
+          <t>-22,36; 21,21</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 94,23</t>
+          <t>40,67; 109,19</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>10,4</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>8,41</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,35</t>
+          <t>-1,08; 1,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,52</t>
+          <t>4,95; 7,77</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -1,35</t>
+          <t>-5,02; -1,62</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,44</t>
+          <t>8,45; 12,13</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,54</t>
+          <t>-2,7; -0,6</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,54</t>
+          <t>7,32; 9,51</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 22,46</t>
+          <t>-14,89; 21,61</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>47,99; 122,91</t>
+          <t>68,58; 129,6</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-28,61; -8,96</t>
+          <t>-29,02; -10,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>20,81; 66,42</t>
+          <t>47,92; 78,73</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-22,25; -4,52</t>
+          <t>-22,21; -5,48</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>36,65; 77,53</t>
+          <t>60,05; 85,97</t>
         </is>
       </c>
     </row>
